--- a/config.xlsx
+++ b/config.xlsx
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4381</v>
+        <v>1.0197</v>
       </c>
     </row>
     <row r="7">

--- a/config.xlsx
+++ b/config.xlsx
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.0197</v>
+        <v>0.3399</v>
       </c>
     </row>
     <row r="7">
